--- a/Zoomlion/ZA10RJE.xlsx
+++ b/Zoomlion/ZA10RJE.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,33 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E321"/>
+  <dimension ref="A1:F331"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Material No.</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Qty</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Item and Spec</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Remark</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Section</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Models</t>
         </is>
       </c>
     </row>
@@ -463,6 +480,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -484,6 +506,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -505,6 +532,11 @@
           <t>Work Platform 00773200100000000</t>
         </is>
       </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -526,6 +558,11 @@
           <t>Work Platform 00773200100000000</t>
         </is>
       </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -547,6 +584,11 @@
           <t>Work Platform 00773200100000000</t>
         </is>
       </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -568,6 +610,11 @@
           <t>Work Platform 00773200100000000</t>
         </is>
       </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -589,6 +636,11 @@
           <t>Work Platform 00773200100000000</t>
         </is>
       </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -610,6 +662,11 @@
           <t>Work Platform 00773200100000000</t>
         </is>
       </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -631,6 +688,11 @@
           <t>Work Platform 00773200100000000</t>
         </is>
       </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -652,6 +714,11 @@
           <t>Work Platform 00773200100000000</t>
         </is>
       </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -673,6 +740,11 @@
           <t>Jib 00773200200000000; Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -694,6 +766,11 @@
           <t>Jib 00773200200000000</t>
         </is>
       </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -715,6 +792,11 @@
           <t>Jib 00773200200000000</t>
         </is>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -736,6 +818,11 @@
           <t>Jib 00773200200000000</t>
         </is>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -757,6 +844,11 @@
           <t>Jib 00773200200000000</t>
         </is>
       </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -778,6 +870,11 @@
           <t>Jib 00773200200000000</t>
         </is>
       </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -799,6 +896,11 @@
           <t>Jib 00773200200000000</t>
         </is>
       </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -820,6 +922,11 @@
           <t>Jib 00773200200000000</t>
         </is>
       </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -841,6 +948,11 @@
           <t>Jib 00773200200000000</t>
         </is>
       </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -862,6 +974,11 @@
           <t>Jib 00773200200000000</t>
         </is>
       </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -883,6 +1000,11 @@
           <t>Jib 00773200200000000</t>
         </is>
       </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -904,6 +1026,11 @@
           <t>Jib 00773200200000000</t>
         </is>
       </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -925,6 +1052,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -946,6 +1078,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -967,6 +1104,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -988,6 +1130,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1009,6 +1156,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1021,8 +1173,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Platform control valve mounting 
-plate</t>
+          <t>Platform control valve mounting plate</t>
         </is>
       </c>
       <c r="D29" t="inlineStr"/>
@@ -1031,6 +1182,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1052,6 +1208,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1073,6 +1234,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1094,6 +1260,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1115,6 +1286,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1136,6 +1312,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1157,6 +1338,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1178,6 +1364,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1199,6 +1390,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1220,6 +1416,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1241,6 +1442,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1262,6 +1468,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1283,6 +1494,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1304,6 +1520,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1325,6 +1546,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1346,6 +1572,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1367,6 +1598,11 @@
           <t>Upper Boom Assembly 00773200300000000</t>
         </is>
       </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1388,6 +1624,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1409,6 +1650,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1430,6 +1676,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1451,6 +1702,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1472,6 +1728,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1493,6 +1754,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1514,6 +1780,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1535,6 +1806,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1556,6 +1832,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1577,6 +1858,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1598,6 +1884,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1619,6 +1910,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1640,6 +1936,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1652,7 +1953,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seal plateⅠ</t>
+          <t>Seal plateI</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -1661,6 +1962,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1673,7 +1979,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seal plateⅡ</t>
+          <t>Seal plateII</t>
         </is>
       </c>
       <c r="D60" t="inlineStr"/>
@@ -1682,6 +1988,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1703,6 +2014,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1724,6 +2040,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1745,6 +2066,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1766,6 +2092,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1787,6 +2118,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1808,6 +2144,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1829,6 +2170,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1850,6 +2196,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1871,6 +2222,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1892,6 +2248,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1913,6 +2274,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1934,6 +2300,11 @@
           <t>Tower Boom Assembly 00773200400000000</t>
         </is>
       </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1955,6 +2326,11 @@
           <t>Chain System 00773200700000000</t>
         </is>
       </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1976,6 +2352,11 @@
           <t>Chain System 00773200700000000</t>
         </is>
       </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1997,6 +2378,11 @@
           <t>Chain System 00773200700000000</t>
         </is>
       </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2018,6 +2404,11 @@
           <t>Chain System 00773200700000000</t>
         </is>
       </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2039,6 +2430,11 @@
           <t>Chain System 00773200700000000</t>
         </is>
       </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2060,6 +2456,11 @@
           <t>Chain System 00773200700000000</t>
         </is>
       </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2081,6 +2482,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2102,6 +2508,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2123,6 +2534,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2144,6 +2560,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2165,6 +2586,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2186,6 +2612,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2207,6 +2638,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2228,6 +2664,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2249,6 +2690,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2270,6 +2716,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2291,6 +2742,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2312,6 +2768,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2333,6 +2794,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2354,6 +2820,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2375,6 +2846,11 @@
           <t>Turntable 00773200800000000</t>
         </is>
       </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2396,6 +2872,11 @@
           <t>Counterweight 00773201000000000</t>
         </is>
       </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2417,6 +2898,11 @@
           <t>Hood 00773201100000000</t>
         </is>
       </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2438,6 +2924,11 @@
           <t>Hood 00773201100000000</t>
         </is>
       </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2459,6 +2950,11 @@
           <t>Hood 00773201100000000</t>
         </is>
       </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -2480,6 +2976,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2501,6 +3002,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2522,6 +3028,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2543,6 +3054,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2564,6 +3080,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2585,6 +3106,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2606,6 +3132,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -2627,6 +3158,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2648,6 +3184,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -2669,6 +3210,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -2690,6 +3236,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -2711,6 +3262,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2723,12 +3279,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Hub 
-assembly 
-of 
-right 
-steering 
-knuckle</t>
+          <t>Hub assembly of right steering knuckle</t>
         </is>
       </c>
       <c r="D110" t="inlineStr"/>
@@ -2737,6 +3288,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -2749,10 +3305,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hub  assembly  of 
-left 
-steering 
-knuckle</t>
+          <t>Hub  assembly  of left steering knuckle</t>
         </is>
       </c>
       <c r="D111" t="inlineStr"/>
@@ -2761,6 +3314,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -2782,6 +3340,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2803,6 +3366,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -2824,6 +3392,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -2845,6 +3418,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2866,6 +3444,11 @@
           <t>Chassis 00773202800000000</t>
         </is>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -2878,10 +3461,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Platform 
-electric 
-console 
-assembly</t>
+          <t>Platform electric console assembly</t>
         </is>
       </c>
       <c r="D117" t="inlineStr"/>
@@ -2890,74 +3470,94 @@
           <t>Work Platform 00773200100000000</t>
         </is>
       </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>00773400100401030</t>
+          <t>00773206200234010</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Adjustable pad</t>
+          <t>Battery series circuit</t>
         </is>
       </c>
       <c r="D118" t="inlineStr"/>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000</t>
+          <t>Power Line 00773206200230050</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>00773400130401040</t>
+          <t>00773206200234020</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Block I</t>
+          <t>Connect the positive electrode of the battery to the group plate B+</t>
         </is>
       </c>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Power Line 00773206200230050</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>00773400130401050</t>
+          <t>00773206200234030</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Block II</t>
+          <t>Connect the negative pole of the battery to the manual switch</t>
         </is>
       </c>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Power Line 00773206200230050</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>00773400130401060</t>
+          <t>00773206200234040</t>
         </is>
       </c>
       <c r="B121" t="n">
@@ -2965,20 +3565,25 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Block III</t>
+          <t>Manual switch and group plate B-line</t>
         </is>
       </c>
       <c r="D121" t="inlineStr"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Power Line 00773206200230050</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>00773400130401070</t>
+          <t>00773206200234050</t>
         </is>
       </c>
       <c r="B122" t="n">
@@ -2986,83 +3591,103 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Round head bolt</t>
+          <t>Connect the left driver P- and function pump D1</t>
         </is>
       </c>
       <c r="D122" t="inlineStr"/>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Power Line 00773206200230050</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>00773400200001010</t>
+          <t>00773206200234060</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Function pump insurance and function pump A1 connection</t>
         </is>
       </c>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000</t>
+          <t>Power Line 00773206200230050</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>00773400200001070</t>
+          <t>00773400100401030</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Stop pin</t>
+          <t>Adjustable pad</t>
         </is>
       </c>
       <c r="D124" t="inlineStr"/>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000; Chassis 00773202800000000</t>
+          <t>Jib 00773200200000000</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>00773400300001120</t>
+          <t>00773400130401040</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Adjustable gasket Ⅲ Tp1</t>
+          <t>Block I</t>
         </is>
       </c>
       <c r="D125" t="inlineStr"/>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>00773400300001200</t>
+          <t>00773400130401050</t>
         </is>
       </c>
       <c r="B126" t="n">
@@ -3070,41 +3695,51 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Stop pin</t>
+          <t>Block II</t>
         </is>
       </c>
       <c r="D126" t="inlineStr"/>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000; Tower Boom Assembly 00773200400000000; Chassis 00773202800000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>00773400300001210</t>
+          <t>00773400130401060</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Block III</t>
         </is>
       </c>
       <c r="D127" t="inlineStr"/>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>00773400310001200</t>
+          <t>00773400130401070</t>
         </is>
       </c>
       <c r="B128" t="n">
@@ -3112,230 +3747,285 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Small cover</t>
+          <t>Round head bolt</t>
         </is>
       </c>
       <c r="D128" t="inlineStr"/>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>00773400312600000</t>
+          <t>00773400200001010</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Slider assembly</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="D129" t="inlineStr"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000</t>
+          <t>Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>00773400312800000</t>
+          <t>00773400200001070</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Slider assembly</t>
+          <t>Stop pin</t>
         </is>
       </c>
       <c r="D130" t="inlineStr"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000</t>
+          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>00773402800001260</t>
+          <t>00773400300001120</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Adjustable gasket III Tp1</t>
         </is>
       </c>
       <c r="D131" t="inlineStr"/>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>00773402820001030</t>
+          <t>00773400300001200</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Steering pull rod gasket</t>
+          <t>Stop pin</t>
         </is>
       </c>
       <c r="D132" t="inlineStr"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Jib 00773200200000000; Tower Boom Assembly 00773200400000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>00773402820001061</t>
+          <t>00773400300001210</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Angle sensor protective hood</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="D133" t="inlineStr"/>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>00773402820001070</t>
+          <t>00773400310001200</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Steering knuckle main pin</t>
+          <t>Small cover</t>
         </is>
       </c>
       <c r="D134" t="inlineStr"/>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>00773402820001090</t>
+          <t>00773400312600000</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Charger port protective box</t>
+          <t>Slider assembly</t>
         </is>
       </c>
       <c r="D135" t="inlineStr"/>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>00773402820001110</t>
+          <t>00773400312800000</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Slider assembly</t>
         </is>
       </c>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>00773406300201010</t>
+          <t>00773402800001260</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Gasket</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="D137" t="inlineStr"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>00773700200001010</t>
+          <t>00773402820001030</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bearing</t>
+          <t>Steering pull rod gasket</t>
         </is>
       </c>
       <c r="D138" t="inlineStr"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>00773700300001270</t>
+          <t>00773402820001061</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -3343,146 +4033,181 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Sensor cover</t>
+          <t>Angle sensor protective hood</t>
         </is>
       </c>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>00773700302400000</t>
+          <t>00773402820001070</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Protective cover</t>
+          <t>Steering knuckle main pin</t>
         </is>
       </c>
       <c r="D140" t="inlineStr"/>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>00773700400001290</t>
+          <t>00773402820001090</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Snap-gauge; Card board</t>
+          <t>Charger port protective box</t>
         </is>
       </c>
       <c r="D141" t="inlineStr"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000; Turntable 00773200800000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>00773700810001050</t>
+          <t>00773402820001110</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Shelf</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="D142" t="inlineStr"/>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>00773700810800000</t>
+          <t>00773406300201010</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Manual valve tools</t>
+          <t>Gasket</t>
         </is>
       </c>
       <c r="D143" t="inlineStr"/>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>00773702800001380</t>
+          <t>00773700200001010</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Stop pin</t>
+          <t>Bearing</t>
         </is>
       </c>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>00775802800001250</t>
+          <t>00773700300001270</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Stop pin</t>
+          <t>Sensor cover</t>
         </is>
       </c>
       <c r="D145" t="inlineStr"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>1010201709</t>
+          <t>00773700302400000</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -3490,167 +4215,207 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Rotary actuator</t>
+          <t>Protective cover</t>
         </is>
       </c>
       <c r="D146" t="inlineStr"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000</t>
+          <t>Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>1010201710</t>
+          <t>00773700400001290</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Rotary actuator</t>
+          <t>Snap-gauge; Card board</t>
         </is>
       </c>
       <c r="D147" t="inlineStr"/>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000</t>
+          <t>Jib 00773200200000000; Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>1010305591</t>
+          <t>00773700810001050</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Balance valve</t>
+          <t>Shelf</t>
         </is>
       </c>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Tower Boom Balance Valve Assembly 00773205200600000</t>
+          <t>Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>1010306020</t>
+          <t>00773700810800000</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Balance valve</t>
+          <t>Manual valve tools</t>
         </is>
       </c>
       <c r="D149" t="inlineStr"/>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Main Boom Lifting Balance Valve Installation 00773205201000000; Main Boom Telescopic Balance Valve Installation 00773205200800000; Jib Lifting Balance Valve Assembly 00773205201000000</t>
+          <t>Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>1010307852</t>
+          <t>00773702800001380</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Main valve assembly</t>
+          <t>Stop pin</t>
         </is>
       </c>
       <c r="D150" t="inlineStr"/>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Main valve Assembly of Turntable 00773205201800000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>1010307853</t>
+          <t>00775802800001250</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Platform control valve</t>
+          <t>Stop pin</t>
         </is>
       </c>
       <c r="D151" t="inlineStr"/>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Main Boom Platform Valve Installation 00773205200800000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>1010601138</t>
+          <t>1010201709</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>High pressure filter</t>
+          <t>Rotary actuator</t>
         </is>
       </c>
       <c r="D152" t="inlineStr"/>
       <c r="E152" t="inlineStr">
         <is>
-          <t>High Pressure Filter installation of Turntable 00773205201800000; Low Pressure Filter Installation of Turntable 00773205201800000</t>
+          <t>Jib 00773200200000000</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1011200193</t>
+          <t>1010201710</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>High pressure articulating joint</t>
+          <t>Rotary actuator</t>
         </is>
       </c>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Main Boom Lifting Balance Valve Installation 00773205201000000; Tower Boom Balance Valve Assembly 00773205200600000; Main Boom Telescopic Balance Valve Installation 00773205200800000; Jib Lifting Balance Valve Assembly 00773205201000000</t>
+          <t>Jib 00773200200000000</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1019901763</t>
+          <t>1010305591</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -3658,66 +4423,77 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Power unit</t>
+          <t>Balance valve</t>
         </is>
       </c>
       <c r="D154" t="inlineStr"/>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Power Unit Assembly of Turntable 00773205201800000</t>
+          <t>Tower Boom Balance Valve Assembly 00773205200600000</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>1020103232</t>
+          <t>1010306020</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Sheath</t>
-        </is>
-      </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>Speed sensor</t>
-        </is>
-      </c>
+          <t>Balance valve</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr"/>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Chassis Wires 00773206200230020</t>
+          <t>Main Boom Lifting Balance Valve Installation 00773205201000000; Main Boom Telescopic Balance Valve Installation 00773205200800000; Jib Lifting Balance Valve Assembly 00773205201000000</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1020103903</t>
+          <t>1010307852</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Controller</t>
+          <t>Main valve assembly</t>
         </is>
       </c>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773206200220000; Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Main valve Assembly of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1020103955</t>
+          <t>1010307853</t>
         </is>
       </c>
       <c r="B157" t="n">
@@ -3725,175 +4501,211 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Connector assembly</t>
+          <t>Platform control valve</t>
         </is>
       </c>
       <c r="D157" t="inlineStr"/>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Main Boom Platform Valve Installation 00773205200800000</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>1020201651</t>
+          <t>1010601138</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Display</t>
+          <t>High pressure filter</t>
         </is>
       </c>
       <c r="D158" t="inlineStr"/>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773206200220000</t>
+          <t>High Pressure Filter installation of Turntable 00773205201800000; Low Pressure Filter Installation of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1020303202</t>
+          <t>1011200193</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Relay</t>
-        </is>
-      </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>Ignition relay; Main relay</t>
-        </is>
-      </c>
+          <t>High pressure articulating joint</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr"/>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773206200220000; Chassis Wires 00773206200230020</t>
+          <t>Main Boom Lifting Balance Valve Installation 00773205201000000; Tower Boom Balance Valve Assembly 00773205200600000; Main Boom Telescopic Balance Valve Installation 00773205200800000; Jib Lifting Balance Valve Assembly 00773205201000000</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>1020404399</t>
+          <t>1019901763</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Alarm light</t>
+          <t>Power unit</t>
         </is>
       </c>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Turntable cable 00773206200230010</t>
+          <t>Power Unit Assembly of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1020404405</t>
+          <t>1020103232</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Flash buzzer</t>
-        </is>
-      </c>
-      <c r="D161" t="inlineStr"/>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Speed sensor</t>
+        </is>
+      </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Chassis Wires 00773206200230020</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>1020405061</t>
+          <t>1020103903</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Alarm indicator panel</t>
+          <t>Controller</t>
         </is>
       </c>
       <c r="D162" t="inlineStr"/>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Turntable Electrical Control Box Assembly 00773206200220000; Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>1020509007</t>
+          <t>1020103955</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Button seat</t>
+          <t>Connector assembly</t>
         </is>
       </c>
       <c r="D163" t="inlineStr"/>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773206200220000; Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>1020519658</t>
+          <t>1020201651</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Emergency stop button</t>
-        </is>
-      </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>Emergency stop switch</t>
-        </is>
-      </c>
+          <t>Display</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr"/>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773206200220000; Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Turntable Electrical Control Box Assembly 00773206200220000</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>1020520083</t>
+          <t>1020202207</t>
         </is>
       </c>
       <c r="B165" t="n">
@@ -3901,75 +4713,81 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Toggle switch</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>Drive orientation</t>
-        </is>
-      </c>
+          <t>Driver assembly</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr"/>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Power Line 00773206200230050</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1020520084</t>
+          <t>1020303202</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Toggle switch</t>
+          <t>Relay</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Emergency power and 
-enable; Jib rotation; Boom telescopic; Boom lifting; Tower boom lifting; Turntable rotation; Jib lifting; Platform rotation; Platform leveling; Travel speed control; Platform leveling control; Main boom telescopic; Platform rotary switch</t>
+          <t>Ignition relay; Main relay</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773206200220000; Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Turntable Electrical Control Box Assembly 00773206200220000; Chassis Wires 00773206200230020</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>1020520136</t>
+          <t>1020404399</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Toggle switch</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>Illumination; Horn</t>
-        </is>
-      </c>
+          <t>Alarm light</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr"/>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Turntable cable 00773206200230010</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>1020520943</t>
+          <t>1020404405</t>
         </is>
       </c>
       <c r="B168" t="n">
@@ -3977,20 +4795,25 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Key switch</t>
+          <t>Flash buzzer</t>
         </is>
       </c>
       <c r="D168" t="inlineStr"/>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773206200220000</t>
+          <t>Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>1020520993</t>
+          <t>1020405061</t>
         </is>
       </c>
       <c r="B169" t="n">
@@ -3998,7 +4821,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Boom handle</t>
+          <t>Alarm indicator panel</t>
         </is>
       </c>
       <c r="D169" t="inlineStr"/>
@@ -4007,32 +4830,42 @@
           <t>Platform Electrical Box Assembly 00773206200210000</t>
         </is>
       </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>1020520994</t>
+          <t>1020509007</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Drive control handle</t>
+          <t>Button seat</t>
         </is>
       </c>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Turntable Electrical Control Box Assembly 00773206200220000; Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>1020521022</t>
+          <t>1020519658</t>
         </is>
       </c>
       <c r="B171" t="n">
@@ -4040,87 +4873,119 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Foot switch</t>
-        </is>
-      </c>
-      <c r="D171" t="inlineStr"/>
+          <t>Emergency stop button</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Emergency stop switch</t>
+        </is>
+      </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000; Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+          <t>Turntable Electrical Control Box Assembly 00773206200220000; Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1020604934</t>
+          <t>1020520083</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Fuse terminal</t>
-        </is>
-      </c>
-      <c r="D172" t="inlineStr"/>
+          <t>Toggle switch</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Drive orientation</t>
+        </is>
+      </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773206200220000</t>
+          <t>Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1020700540</t>
+          <t>1020520084</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Terminal resistance</t>
-        </is>
-      </c>
-      <c r="D173" t="inlineStr"/>
+          <t>Toggle switch</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Emergency power and enable; Jib rotation; Boom telescopic; Boom lifting; Tower boom lifting; Turntable rotation; Jib lifting; Platform rotation; Platform leveling; Travel speed control; Platform leveling control; Main boom telescopic; Platform rotary switch</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Boom wires 00773206200230030</t>
+          <t>Turntable Electrical Control Box Assembly 00773206200220000; Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>1020700951</t>
+          <t>1020520136</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Sheath</t>
+          <t>Toggle switch</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Leveling down valve; Leveling up valve; Turntable right-turn valve; Turntable left-turn valve; Boom extending valve; Boom retracting valve; Boom lowering valve; Boom lifting valve; Tower boom lifting valve; Tower boom lowering valve; Front wheel left-turn valve; Front wheel right-turn valve; Proportion control valve; Charger; Jib lifting valve; Jib lowering valve; Jib right-swing valve; Jib left-swing valve; Platform left-swing valve; Platform right-swing valve</t>
+          <t>Illumination; Horn</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Turntable cable 00773206200230010; Chassis Wires 00773206200230020; Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+          <t>Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>1020703394</t>
+          <t>1020520943</t>
         </is>
       </c>
       <c r="B175" t="n">
@@ -4128,116 +4993,129 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Deutsch connector</t>
-        </is>
-      </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>Cable chain harness</t>
-        </is>
-      </c>
+          <t>Key switch</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr"/>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Turntable Electrical Control Box Assembly 00773206200220000</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>1020705826</t>
+          <t>1020520993</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Diode terminal</t>
+          <t>Boom handle</t>
         </is>
       </c>
       <c r="D176" t="inlineStr"/>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773206200220000</t>
+          <t>Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>1020706399</t>
+          <t>1020520994</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Sheath</t>
-        </is>
-      </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>ECU cable; Cable lower connector</t>
-        </is>
-      </c>
+          <t>Drive control handle</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr"/>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Chassis Wires 00773206200230020; Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+          <t>Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1020706505</t>
+          <t>1020521022</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>connector</t>
-        </is>
-      </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>ECU cable</t>
-        </is>
-      </c>
+          <t>Foot switch</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr"/>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Turntable cable 00773206200230010; Boom wires 00773206200230030</t>
+          <t>Work Platform 00773200100000000; Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>1021404016</t>
+          <t>1020604934</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Load cell</t>
+          <t>Fuse terminal</t>
         </is>
       </c>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+          <t>Turntable Electrical Control Box Assembly 00773206200220000</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>1021404018</t>
+          <t>1020700540</t>
         </is>
       </c>
       <c r="B180" t="n">
@@ -4245,41 +5123,55 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Frame angle sensor</t>
+          <t>Terminal resistance</t>
         </is>
       </c>
       <c r="D180" t="inlineStr"/>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Chassis Wires 00773206200230020</t>
+          <t>Boom wires 00773206200230030</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>1021404019</t>
+          <t>1020700951</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Boom leveling angle sensor</t>
-        </is>
-      </c>
-      <c r="D181" t="inlineStr"/>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Leveling down valve; Leveling up valve; Turntable right-turn valve; Turntable left-turn valve; Boom extending valve; Boom retracting valve; Boom lowering valve; Boom lifting valve; Tower boom lifting valve; Tower boom lowering valve; Front wheel left-turn valve; Front wheel right-turn valve; Proportion control valve; Charger; Jib lifting valve; Jib lowering valve; Jib right-swing valve; Jib left-swing valve; Platform left-swing valve; Platform right-swing valve</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Boom wires 00773206200230030</t>
+          <t>Turntable cable 00773206200230010; Chassis Wires 00773206200230020; Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>1022200446</t>
+          <t>1020703394</t>
         </is>
       </c>
       <c r="B182" t="n">
@@ -4287,49 +5179,55 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Sheath</t>
+          <t>Deutsch connector</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Platform connector</t>
+          <t>Cable chain harness</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+          <t>Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>1022200683</t>
+          <t>1020705826</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Sheath</t>
-        </is>
-      </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>Turntable electric control box</t>
-        </is>
-      </c>
+          <t>Diode terminal</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr"/>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Turntable cable 00773206200230010</t>
+          <t>Turntable Electrical Control Box Assembly 00773206200220000</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>1022270089</t>
+          <t>1020706399</t>
         </is>
       </c>
       <c r="B184" t="n">
@@ -4337,24 +5235,29 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Sheath; connector</t>
+          <t>Sheath</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Turntable electric control box</t>
+          <t>ECU cable; Cable lower connector</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Turntable cable 00773206200230010; Boom wires 00773206200230030</t>
+          <t>Chassis Wires 00773206200230020; Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>1022399012</t>
+          <t>1020706505</t>
         </is>
       </c>
       <c r="B185" t="n">
@@ -4362,20 +5265,29 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Line slot</t>
-        </is>
-      </c>
-      <c r="D185" t="inlineStr"/>
+          <t>connector</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>ECU cable</t>
+        </is>
+      </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Turntable cable 00773206200230010; Boom wires 00773206200230030</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>1029802085</t>
+          <t>1020999056</t>
         </is>
       </c>
       <c r="B186" t="n">
@@ -4383,70 +5295,85 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Nylon plug</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Power Line 00773206200230050</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>1029900385</t>
+          <t>1020999057</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Steering angle sensor</t>
+          <t>Battery</t>
         </is>
       </c>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Chassis Wires 00773206200230020</t>
+          <t>Power Line 00773206200230050</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>1029900398</t>
+          <t>1021404016</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Load cell</t>
         </is>
       </c>
       <c r="D188" t="inlineStr"/>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Turntable cable 00773206200230010</t>
+          <t>Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>1029900400</t>
+          <t>1021404018</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Terminal</t>
+          <t>Frame angle sensor</t>
         </is>
       </c>
       <c r="D189" t="inlineStr"/>
@@ -4455,40 +5382,46 @@
           <t>Chassis Wires 00773206200230020</t>
         </is>
       </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1029902113</t>
+          <t>1021404019</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Sheath</t>
-        </is>
-      </c>
-      <c r="D190" t="inlineStr">
-        <is>
-          <t>Temperature</t>
-        </is>
-      </c>
+          <t>Boom leveling angle sensor</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr"/>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Chassis Wires 00773206200230020</t>
+          <t>Boom wires 00773206200230030</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>1029902114</t>
+          <t>1022200446</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C191" t="inlineStr">
         <is>
@@ -4497,19 +5430,24 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Electromagnetic brake</t>
+          <t>Platform connector</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Chassis Wires 00773206200230020</t>
+          <t>Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1029903711</t>
+          <t>1022200683</t>
         </is>
       </c>
       <c r="B192" t="n">
@@ -4522,48 +5460,62 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Upper connector of chain</t>
+          <t>Turntable electric control box</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+          <t>Turntable cable 00773206200230010</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>1029904980</t>
+          <t>1022270089</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Terminal</t>
-        </is>
-      </c>
-      <c r="D193" t="inlineStr"/>
+          <t>Sheath; connector</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>Turntable electric control box</t>
+        </is>
+      </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Turntable Electrical Control Box Assembly 00773206200220000; Platform Electrical Box Assembly 00773206200210000</t>
+          <t>Turntable cable 00773206200230010; Boom wires 00773206200230030</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1029905392</t>
+          <t>1022399012</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Fuse terminal</t>
+          <t>Line slot</t>
         </is>
       </c>
       <c r="D194" t="inlineStr"/>
@@ -4572,123 +5524,146 @@
           <t>Platform Electrical Box Assembly 00773206200210000</t>
         </is>
       </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>1029906298</t>
+          <t>1029802085</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Limit switch- Tower 
-boom stowed 1; Turntable angle limit 
-switch; Limit switch- Tower 
-boom stowed 2; Boom length limit switch 1; Boom length limit switch 2; Anti-crushing switch</t>
+          <t>Nylon plug</t>
         </is>
       </c>
       <c r="D195" t="inlineStr"/>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Turntable cable 00773206200230010; Boom wires 00773206200230030; Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+          <t>Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1029907627</t>
+          <t>1029900385</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Load cell</t>
+          <t>Steering angle sensor</t>
         </is>
       </c>
       <c r="D196" t="inlineStr"/>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Chassis Wires 00773206200230020</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>1030202593</t>
+          <t>1029900398</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Rotary reducer</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="D197" t="inlineStr"/>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Slewing Mechanism 00773200900000000</t>
+          <t>Turntable cable 00773206200230010</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>1030202594</t>
+          <t>1029900400</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Travel reducer</t>
+          <t>Terminal</t>
         </is>
       </c>
       <c r="D198" t="inlineStr"/>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Chassis Wires 00773206200230020</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1030800871</t>
+          <t>1029900667</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Tire</t>
-        </is>
-      </c>
-      <c r="D199" t="inlineStr">
-        <is>
-          <t>ML22×7-20200814LT</t>
-        </is>
-      </c>
+          <t>Main power switch</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr"/>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Power Line 00773206200230050</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>1040000096</t>
+          <t>1029902113</t>
         </is>
       </c>
       <c r="B200" t="n">
@@ -4696,309 +5671,339 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Bolt 
-  M6×12-8.8</t>
-        </is>
-      </c>
-      <c r="D200" t="inlineStr"/>
+          <t>Sheath</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Temperature</t>
+        </is>
+      </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000</t>
+          <t>Chassis Wires 00773206200230020</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>1040001631</t>
+          <t>1029902114</t>
         </is>
       </c>
       <c r="B201" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Bolt M6×20-A2-70</t>
+          <t>Sheath</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>GB/T5783-2000</t>
+          <t>Electromagnetic brake</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Chassis Wires 00773206200230020</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>1040001640</t>
+          <t>1029903711</t>
         </is>
       </c>
       <c r="B202" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Bolt 
-  M6×25-A2-70; Bolt M6×25-A2-70</t>
+          <t>Sheath</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>GB/T5783-2000</t>
+          <t>Upper connector of chain</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000; Turntable 00773200800000000</t>
+          <t>Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>1040001703</t>
+          <t>1029904980</t>
         </is>
       </c>
       <c r="B203" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Bolt M12×65-10.9</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>GB/T5782</t>
-        </is>
-      </c>
+          <t>Terminal</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr"/>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Turntable Electrical Control Box Assembly 00773206200220000; Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>1040002433</t>
+          <t>1029905392</t>
         </is>
       </c>
       <c r="B204" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Bolt M10×20-8.8</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>GB/T5783; GB/T5783-2000</t>
-        </is>
-      </c>
+          <t>Fuse terminal</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr"/>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000; Upper Boom Assembly 00773200300000000; Turntable 00773200800000000; Chassis 00773202800000000</t>
+          <t>Platform Electrical Box Assembly 00773206200210000</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1040002434</t>
+          <t>1029906298</t>
         </is>
       </c>
       <c r="B205" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Bolt M10×25-8.8</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>GB/T5783-2016; GB/T5783-2000</t>
-        </is>
-      </c>
+          <t>Limit switch- Tower boom stowed 1; Turntable angle limit switch; Limit switch- Tower boom stowed 2; Boom length limit switch 1; Boom length limit switch 2; Anti-crushing switch</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000; Turntable 00773200800000000; Chassis 00773202800000000</t>
+          <t>Turntable cable 00773206200230010; Boom wires 00773206200230030; Platform Wires 00773206200230040 Chain Wires Change 00773206200240010</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>1040002436</t>
+          <t>1029907627</t>
         </is>
       </c>
       <c r="B206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Bolt 
-  M12×25-8.8</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>GB/T5783-2000</t>
-        </is>
-      </c>
+          <t>Load cell</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr"/>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>1040002439</t>
+          <t>1030202593</t>
         </is>
       </c>
       <c r="B207" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Bolt M12×40-8.8</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>GB/T5783-2000</t>
-        </is>
-      </c>
+          <t>Rotary reducer</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr"/>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Slewing Mechanism 00773200900000000</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>1040002458</t>
+          <t>1030202594</t>
         </is>
       </c>
       <c r="B208" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Bolt 
-  M8×40-8.8; Bolt M8×40-8.8</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>GB/T5783-2000</t>
-        </is>
-      </c>
+          <t>Travel reducer</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000; Chassis 00773202800000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>1040002555</t>
+          <t>1030800871</t>
         </is>
       </c>
       <c r="B209" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Bolt M6×16-A2-70</t>
+          <t>Tire</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>GB/T5783-2000</t>
+          <t>ML22×7-20200814LT</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Hood 00773201100000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>1040002738</t>
+          <t>1040000096</t>
         </is>
       </c>
       <c r="B210" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Bolt 
-  M6×12-A2-70</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>GB/T5783-2000</t>
-        </is>
-      </c>
+          <t>Bolt M6×12-8.8</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000</t>
+          <t>Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>1040004508</t>
+          <t>1040001631</t>
         </is>
       </c>
       <c r="B211" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Bolt M10×45-8.8</t>
+          <t>Bolt M6×20-A2-70</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>1040004511</t>
+          <t>1040001640</t>
         </is>
       </c>
       <c r="B212" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Bolt 
-  M12×30-8.8</t>
+          <t>Bolt M6×25-A2-70</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -5008,99 +6013,117 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000</t>
+          <t>Upper Boom Assembly 00773200300000000; Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1040004517</t>
+          <t>1040001703</t>
         </is>
       </c>
       <c r="B213" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>Bolt 
-  M8×16-8.8; Bolt M8×16-8.8; Screw M8×16-8.8</t>
+          <t>Bolt M12×65-10.9</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>GB/T5783-2000</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000; Chassis 00773202800000000; Low Pressure Filter Installation of Turntable 00773205201800000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>1040004518</t>
+          <t>1040002433</t>
         </is>
       </c>
       <c r="B214" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Bolt M8×20-8.8; Screw M8×20-8.8</t>
+          <t>Bolt M10×20-8.8</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>GB/T5783-2000</t>
+          <t>GB/T5783; GB/T5783-2000</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000; High Pressure Filter installation of Turntable 00773205201800000</t>
+          <t>Jib 00773200200000000; Upper Boom Assembly 00773200300000000; Turntable 00773200800000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1040004519</t>
+          <t>1040002434</t>
         </is>
       </c>
       <c r="B215" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Bolt 
-  M8×25-8.8; Bolt M8×25-8.8</t>
+          <t>Bolt M10×25-8.8</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>GB/T5783-2000</t>
+          <t>GB/T5783-2016; GB/T5783-2000</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Chain System 00773200700000000; Turntable 00773200800000000</t>
+          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000; Turntable 00773200800000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>1040004521</t>
+          <t>1040002436</t>
         </is>
       </c>
       <c r="B216" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Bolt M8×45-8.8</t>
+          <t>Bolt M12×25-8.8</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -5110,149 +6133,177 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1040004522</t>
+          <t>1040002439</t>
         </is>
       </c>
       <c r="B217" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bolt M8×50-8.8</t>
+          <t>Bolt M12×40-8.8</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1040004553</t>
+          <t>1040002458</t>
         </is>
       </c>
       <c r="B218" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Bolt M6×35-8.8</t>
+          <t>Bolt M8×40-8.8</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1040004565</t>
+          <t>1040002555</t>
         </is>
       </c>
       <c r="B219" t="n">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Bolt 
-  M10×30-8.8-DKL; Bolt M10×30-8.8-DKL</t>
+          <t>Bolt M6×16-A2-70</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>GB/T5783-2016</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000; Turntable 00773200800000000; Chassis 00773202800000000</t>
+          <t>Hood 00773201100000000</t>
+        </is>
+      </c>
+      <c r="F219" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>1040004581</t>
+          <t>1040002738</t>
         </is>
       </c>
       <c r="B220" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Bolt M10×80-8.8</t>
+          <t>Bolt M6×12-A2-70</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000</t>
+          <t>Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>1040004590</t>
+          <t>1040004508</t>
         </is>
       </c>
       <c r="B221" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bolt 
-  M8×14-8.8; Bolt M8×14-8.8</t>
+          <t>Bolt M10×45-8.8</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>GB/T5783-2000</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000; Turntable 00773200800000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1040004591</t>
+          <t>1040004511</t>
         </is>
       </c>
       <c r="B222" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bolt M4×8-8.8</t>
+          <t>Bolt M12×30-8.8</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -5262,49 +6313,57 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000</t>
+          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>1040004605</t>
+          <t>1040004517</t>
         </is>
       </c>
       <c r="B223" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Bolt 
-  M12×75-8.8</t>
+          <t>Bolt M8×16-8.8; Screw M8×16-8.8</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>GB/T5782-2000</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000</t>
+          <t>Upper Boom Assembly 00773200300000000; Chassis 00773202800000000; Low Pressure Filter Installation of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F223" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>1040004619</t>
+          <t>1040004518</t>
         </is>
       </c>
       <c r="B224" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Bolt 
-  M8×35-8.8</t>
+          <t>Bolt M8×20-8.8; Screw M8×20-8.8</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -5314,165 +6373,207 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000</t>
+          <t>Turntable 00773200800000000; High Pressure Filter installation of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>1040004646</t>
+          <t>1040004519</t>
         </is>
       </c>
       <c r="B225" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Bolt M10×15-8.8</t>
+          <t>Bolt M8×25-8.8</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Chain System 00773200700000000; Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F225" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1040004653</t>
+          <t>1040004521</t>
         </is>
       </c>
       <c r="B226" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Bolt M12×30-10.9</t>
+          <t>Bolt M8×45-8.8</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>GB/T5783</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F226" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>1040004657</t>
+          <t>1040004522</t>
         </is>
       </c>
       <c r="B227" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Bolt M12×80-8.8</t>
-        </is>
-      </c>
-      <c r="D227" t="inlineStr"/>
+          <t>Bolt M8×50-8.8</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>GB/T5783</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000</t>
+          <t>Jib 00773200200000000</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>1040004678</t>
+          <t>1040004553</t>
         </is>
       </c>
       <c r="B228" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Door stopper bolt M10×70</t>
-        </is>
-      </c>
-      <c r="D228" t="inlineStr"/>
+          <t>Bolt M6×35-8.8</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>GB/T5783</t>
+        </is>
+      </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F228" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>1040005831</t>
+          <t>1040004565</t>
         </is>
       </c>
       <c r="B229" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Bolt M10×25-DKL</t>
+          <t>Bolt M10×30-8.8-DKL</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>GB/T5789-1986</t>
+          <t>GB/T5783-2016</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Upper Boom Assembly 00773200300000000; Turntable 00773200800000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>1040005846</t>
+          <t>1040004581</t>
         </is>
       </c>
       <c r="B230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Bolt 
-  M12×20-8.8</t>
+          <t>Bolt M10×80-8.8</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>GB/T5783-2000</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000</t>
+          <t>Jib 00773200200000000</t>
+        </is>
+      </c>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>1040005848</t>
+          <t>1040004590</t>
         </is>
       </c>
       <c r="B231" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Bolt M24×70-10.9</t>
+          <t>Bolt M8×14-8.8</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -5482,47 +6583,57 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Counterweight 00773201000000000</t>
+          <t>Tower Boom Assembly 00773200400000000; Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F231" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>1040006354</t>
+          <t>1040004591</t>
         </is>
       </c>
       <c r="B232" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bolt M16×90-10.9</t>
+          <t>Bolt M4×8-8.8</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>GB/T5782-2000</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Slewing Mechanism 00773200900000000</t>
+          <t>Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F232" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>1040006355</t>
+          <t>1040004605</t>
         </is>
       </c>
       <c r="B233" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Bolt M16×100-10.9</t>
+          <t>Bolt M12×75-8.8</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -5532,468 +6643,559 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Slewing Mechanism 00773200900000000</t>
+          <t>Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F233" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>1040006410</t>
+          <t>1040004619</t>
         </is>
       </c>
       <c r="B234" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Bolt M20×240-10.9</t>
+          <t>Bolt M8×35-8.8</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F234" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>1040006411</t>
+          <t>1040004646</t>
         </is>
       </c>
       <c r="B235" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Bolt M24×310-10.9</t>
+          <t>Bolt M10×15-8.8</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>GB/T5782</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F235" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>1040006550</t>
+          <t>1040004653</t>
         </is>
       </c>
       <c r="B236" t="n">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Bolt M16×40-10.9</t>
+          <t>Bolt M12×30-10.9</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>GB/T5783-2000</t>
+          <t>GB/T5783</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Jib 00773200200000000</t>
+        </is>
+      </c>
+      <c r="F236" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>1040006553</t>
+          <t>1040004657</t>
         </is>
       </c>
       <c r="B237" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Bolt M10×25-10.9</t>
-        </is>
-      </c>
-      <c r="D237" t="inlineStr">
-        <is>
-          <t>GB/T70.1</t>
-        </is>
-      </c>
+          <t>Bolt M12×80-8.8</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr"/>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>1040100349</t>
+          <t>1040004678</t>
         </is>
       </c>
       <c r="B238" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Screw    M4×45-8.8</t>
-        </is>
-      </c>
-      <c r="D238" t="inlineStr">
-        <is>
-          <t>GB/T70.1-2000</t>
-        </is>
-      </c>
+          <t>Door stopper bolt M10×70</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr"/>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Chain System 00773200700000000</t>
+          <t>Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F238" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>1040100765</t>
+          <t>1040005831</t>
         </is>
       </c>
       <c r="B239" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Screw M6×20-8.8</t>
+          <t>Bolt M10×25-DKL</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>GB/T70.3-2000</t>
+          <t>GB/T5789-1986</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F239" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>1040100886</t>
+          <t>1040005846</t>
         </is>
       </c>
       <c r="B240" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Screw M8×20-8.8</t>
+          <t>Bolt M12×20-8.8</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
         <is>
-          <t>GB/T70.1-2008</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F240" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>1040101492</t>
+          <t>1040005848</t>
         </is>
       </c>
       <c r="B241" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Screw    M10×25-8.8</t>
+          <t>Bolt M24×70-10.9</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>GB/T70.1-2000</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000</t>
+          <t>Counterweight 00773201000000000</t>
+        </is>
+      </c>
+      <c r="F241" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>1040101567</t>
+          <t>1040006354</t>
         </is>
       </c>
       <c r="B242" t="n">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Screw    M12×35-10.9-DKL</t>
+          <t>Bolt M16×90-10.9</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
         <is>
-          <t>GB/T70.1-2000</t>
+          <t>GB/T5782-2000</t>
         </is>
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000</t>
+          <t>Slewing Mechanism 00773200900000000</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>1040101606</t>
+          <t>1040006355</t>
         </is>
       </c>
       <c r="B243" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Screw    M8×12-8.8</t>
+          <t>Bolt M16×100-10.9</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
         <is>
-          <t>GB/T70.3-2000</t>
+          <t>GB/T5782-2000</t>
         </is>
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000</t>
+          <t>Slewing Mechanism 00773200900000000</t>
+        </is>
+      </c>
+      <c r="F243" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>1040101846</t>
+          <t>1040006410</t>
         </is>
       </c>
       <c r="B244" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Screw</t>
+          <t>Bolt M20×240-10.9</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
         <is>
-          <t>M4×10-8.8</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E244" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F244" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>1040101995</t>
+          <t>1040006411</t>
         </is>
       </c>
       <c r="B245" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Screw</t>
+          <t>Bolt M24×310-10.9</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>GB/T70.1-2000</t>
+          <t>GB/T5782</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Power Unit Assembly of Turntable 00773205201800000</t>
+          <t>Jib 00773200200000000</t>
+        </is>
+      </c>
+      <c r="F245" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>1040102372</t>
+          <t>1040006550</t>
         </is>
       </c>
       <c r="B246" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Hexagon socket cap screws M6×20-A2-70; Hexagon socket cap screws</t>
+          <t>Bolt M16×40-10.9</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
         <is>
-          <t>GB/T70.1-2000</t>
+          <t>GB/T5783-2000</t>
         </is>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000; Turntable 00773200800000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>1040102429</t>
+          <t>1040006553</t>
         </is>
       </c>
       <c r="B247" t="n">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Screw M4×8</t>
-        </is>
-      </c>
-      <c r="D247" t="inlineStr"/>
+          <t>Bolt M10×25-10.9</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>GB/T70.1</t>
+        </is>
+      </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>1040102757</t>
+          <t>1040100349</t>
         </is>
       </c>
       <c r="B248" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Screw    M10×25-8.8</t>
+          <t>Screw    M4×45-8.8</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
         <is>
-          <t>GB/T70.3-2000</t>
+          <t>GB/T70.1-2000</t>
         </is>
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000</t>
+          <t>Chain System 00773200700000000</t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>1040102761</t>
+          <t>1040100765</t>
         </is>
       </c>
       <c r="B249" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Screw M10×20-8.8</t>
+          <t>Screw M6×20-8.8</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
         <is>
-          <t>GB/T70.1-2000</t>
+          <t>GB/T70.3-2000</t>
         </is>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000</t>
+          <t>Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>1040102773</t>
+          <t>1040100886</t>
         </is>
       </c>
       <c r="B250" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Screw M6×40-8.8; Screw    M6×40-8.8</t>
+          <t>Screw M8×20-8.8</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
         <is>
-          <t>GB/T70.1; GB/T70.1-2000</t>
+          <t>GB/T70.1-2008</t>
         </is>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000; Jib 00773200200000000; Chain System 00773200700000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>1040102774</t>
+          <t>1040101492</t>
         </is>
       </c>
       <c r="B251" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Screw M6×15-8.8</t>
+          <t>Screw    M10×25-8.8</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>GB/T70.1</t>
+          <t>GB/T70.1-2000</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>1040102777</t>
+          <t>1040101567</t>
         </is>
       </c>
       <c r="B252" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Screw    M4×50-8.8</t>
+          <t>Screw    M12×35-10.9-DKL</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -6003,64 +7205,79 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Chain System 00773200700000000</t>
+          <t>Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>1040102778</t>
+          <t>1040101606</t>
         </is>
       </c>
       <c r="B253" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Screw    M6×10-8.8; Screw M6×10-8.8</t>
+          <t>Screw    M8×12-8.8</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>GB/T70.1-2000</t>
+          <t>GB/T70.3-2000</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000; Turntable 00773200800000000</t>
+          <t>Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>1040103076</t>
+          <t>1040101846</t>
         </is>
       </c>
       <c r="B254" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Screw M8×16-8.8</t>
+          <t>Screw</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>GB/T70.3</t>
+          <t>M4×10-8.8</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000</t>
+          <t>Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>1040103110</t>
+          <t>1040101995</t>
         </is>
       </c>
       <c r="B255" t="n">
@@ -6068,7 +7285,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Screw M8×10-8.8</t>
+          <t>Screw</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -6078,22 +7295,27 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Power Unit Assembly of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>1040103111</t>
+          <t>1040102372</t>
         </is>
       </c>
       <c r="B256" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Screw M8×16-8.8</t>
+          <t>Hexagon socket cap screws M6×20-A2-70; Hexagon socket cap screws</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -6103,72 +7325,83 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000; Main valve Assembly of Turntable 00773205201800000</t>
+          <t>Tower Boom Assembly 00773200400000000; Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>1040103112</t>
+          <t>1040102429</t>
         </is>
       </c>
       <c r="B257" t="n">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Screw M8×25-8.8; Screw    M8×25-8.8</t>
-        </is>
-      </c>
-      <c r="D257" t="inlineStr">
-        <is>
-          <t>GB/T70.1; GB/T70.1-2000</t>
-        </is>
-      </c>
+          <t>Screw M4×8</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr"/>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000; Tower Boom Assembly 00773200400000000; Chassis 00773202800000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>1040103114</t>
+          <t>1040102757</t>
         </is>
       </c>
       <c r="B258" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Screw M8×45-8.8</t>
+          <t>Screw    M10×25-8.8</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
         <is>
-          <t>GB/T70.1-2000</t>
+          <t>GB/T70.3-2000</t>
         </is>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Main Boom Lifting Balance Valve Installation 00773205201000000; Tower Boom Balance Valve Assembly 00773205200600000; Main Boom Telescopic Balance Valve Installation 00773205200800000; Jib Lifting Balance Valve Assembly 00773205201000000</t>
+          <t>Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>1040103302</t>
+          <t>1040102761</t>
         </is>
       </c>
       <c r="B259" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Screw    M8×22-10.9</t>
+          <t>Screw M10×20-8.8</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -6178,91 +7411,109 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Tower Boom Assembly 00773200400000000</t>
+          <t>Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F259" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>1040103558</t>
+          <t>1040102773</t>
         </is>
       </c>
       <c r="B260" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Screw M8×25-8.8</t>
+          <t>Screw M6×40-8.8; Screw    M6×40-8.8</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>GB/T70.3-2008</t>
+          <t>GB/T70.1; GB/T70.1-2000</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000</t>
+          <t>Work Platform 00773200100000000; Jib 00773200200000000; Chain System 00773200700000000</t>
+        </is>
+      </c>
+      <c r="F260" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>1040200113</t>
+          <t>1040102774</t>
         </is>
       </c>
       <c r="B261" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Nut 
-  M10-8; Nut M10-8</t>
+          <t>Screw M6×15-8.8</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>GB/T6170-2000</t>
+          <t>GB/T70.1</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000; Chassis 00773202800000000; Power Unit Assembly of Turntable 00773205201800000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F261" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>1040200503</t>
+          <t>1040102777</t>
         </is>
       </c>
       <c r="B262" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Nut M8-8; Nut 
-  M8-8</t>
+          <t>Screw    M4×50-8.8</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>GB/T889.1; GB/T889.1-2000</t>
+          <t>GB/T70.1-2000</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000; Upper Boom Assembly 00773200300000000; Chain System 00773200700000000; Chassis 00773202800000000</t>
+          <t>Chain System 00773200700000000</t>
+        </is>
+      </c>
+      <c r="F262" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>1040200504</t>
+          <t>1040102778</t>
         </is>
       </c>
       <c r="B263" t="n">
@@ -6270,209 +7521,247 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Nut M10-8</t>
+          <t>Screw    M6×10-8.8; Screw M6×10-8.8</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
         <is>
-          <t>GB/T889.1</t>
+          <t>GB/T70.1-2000</t>
         </is>
       </c>
       <c r="E263" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000; Jib 00773200200000000</t>
+          <t>Upper Boom Assembly 00773200300000000; Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F263" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>1040200507</t>
+          <t>1040103076</t>
         </is>
       </c>
       <c r="B264" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Nut M12-8</t>
+          <t>Screw M8×16-8.8</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
         <is>
-          <t>GB/T889.1-2000</t>
+          <t>GB/T70.3</t>
         </is>
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000</t>
+          <t>Jib 00773200200000000</t>
+        </is>
+      </c>
+      <c r="F264" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>1040200741</t>
+          <t>1040103110</t>
         </is>
       </c>
       <c r="B265" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Nut M20-10</t>
+          <t>Screw M8×10-8.8</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
         <is>
-          <t>GB/T889.1</t>
+          <t>GB/T70.1-2000</t>
         </is>
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F265" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>1040201089</t>
+          <t>1040103111</t>
         </is>
       </c>
       <c r="B266" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Nut 
-  M8-8</t>
+          <t>Screw M8×16-8.8</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>GB/T6170-2000</t>
+          <t>GB/T70.1-2000</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000</t>
+          <t>Turntable 00773200800000000; Main valve Assembly of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F266" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>1040201111</t>
+          <t>1040103112</t>
         </is>
       </c>
       <c r="B267" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Nut M24-10</t>
+          <t>Screw M8×25-8.8; Screw    M8×25-8.8</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
         <is>
-          <t>GB/T889</t>
+          <t>GB/T70.1; GB/T70.1-2000</t>
         </is>
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000</t>
+          <t>Work Platform 00773200100000000; Tower Boom Assembly 00773200400000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F267" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>1040201163</t>
+          <t>1040103114</t>
         </is>
       </c>
       <c r="B268" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Nut M12-10</t>
+          <t>Screw M8×45-8.8</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
         <is>
-          <t>GB/T889.1</t>
+          <t>GB/T70.1-2000</t>
         </is>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Main Boom Lifting Balance Valve Installation 00773205201000000; Tower Boom Balance Valve Assembly 00773205200600000; Main Boom Telescopic Balance Valve Installation 00773205200800000; Jib Lifting Balance Valve Assembly 00773205201000000</t>
+        </is>
+      </c>
+      <c r="F268" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>1040201381</t>
+          <t>1040103302</t>
         </is>
       </c>
       <c r="B269" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Nut M12-8</t>
+          <t>Screw    M8×22-10.9</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
         <is>
-          <t>GB/T6170</t>
+          <t>GB/T70.1-2000</t>
         </is>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F269" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>1040201772</t>
+          <t>1040103558</t>
         </is>
       </c>
       <c r="B270" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>Nut 
-  M4-A2-70; Nut M4-A2-70</t>
+          <t>Screw M8×25-8.8</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
         <is>
-          <t>GB/T6170-2000</t>
+          <t>GB/T70.3-2008</t>
         </is>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Chain System 00773200700000000; Chassis 00773202800000000</t>
+          <t>Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F270" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>1040201865</t>
+          <t>1040200113</t>
         </is>
       </c>
       <c r="B271" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Nut M6-8</t>
+          <t>Nut M10-8</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -6482,392 +7771,469 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Chain System 00773200700000000</t>
+          <t>Turntable 00773200800000000; Chassis 00773202800000000; Power Unit Assembly of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F271" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>1040201896</t>
+          <t>1040200503</t>
         </is>
       </c>
       <c r="B272" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Nut M6-8; Nut 
-  M6-8</t>
+          <t>Nut M8-8</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
         <is>
-          <t>GB/T889.1; GB/T889.1-2015</t>
+          <t>GB/T889.1; GB/T889.1-2000</t>
         </is>
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000; Upper Boom Assembly 00773200300000000</t>
+          <t>Work Platform 00773200100000000; Upper Boom Assembly 00773200300000000; Chain System 00773200700000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F272" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>1040201902</t>
+          <t>1040200504</t>
         </is>
       </c>
       <c r="B273" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Nut M6-6</t>
+          <t>Nut M10-8</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
         <is>
-          <t>GB/T802</t>
+          <t>GB/T889.1</t>
         </is>
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Work Platform 00773200100000000; Jib 00773200200000000</t>
+        </is>
+      </c>
+      <c r="F273" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>1040202280</t>
+          <t>1040200507</t>
         </is>
       </c>
       <c r="B274" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Nut M24-05-DKL</t>
+          <t>Nut M12-8</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
         <is>
-          <t>GB/T6181-1986</t>
+          <t>GB/T889.1-2000</t>
         </is>
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F274" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>1040202296</t>
+          <t>1040200741</t>
         </is>
       </c>
       <c r="B275" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Nut 
-  5/8-18UNF-10(Spiralock)</t>
+          <t>Nut M20-10</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>ANSIB18.2.2-2015</t>
+          <t>GB/T889.1</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F275" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>1040202297</t>
+          <t>1040201089</t>
         </is>
       </c>
       <c r="B276" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Nut 
-  M16×1.5-10 (Spiralock)</t>
+          <t>Nut M8-8</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
         <is>
-          <t>GB/T6177.2-2000</t>
+          <t>GB/T6170-2000</t>
         </is>
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F276" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>1040300051</t>
+          <t>1040201111</t>
         </is>
       </c>
       <c r="B277" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Washer 6-200HV</t>
+          <t>Nut M24-10</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
         <is>
-          <t>GB/T97.1-2002</t>
+          <t>GB/T889</t>
         </is>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Main Boom Platform Valve Installation 00773205200800000</t>
+          <t>Jib 00773200200000000</t>
+        </is>
+      </c>
+      <c r="F277" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>1040300062</t>
+          <t>1040201163</t>
         </is>
       </c>
       <c r="B278" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Washer 6</t>
+          <t>Nut M12-10</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>GB/T93-1987</t>
+          <t>GB/T889.1</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Main Boom Platform Valve Installation 00773205200800000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F278" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>1040300735</t>
+          <t>1040201381</t>
         </is>
       </c>
       <c r="B279" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Washer 6-200HV</t>
+          <t>Nut M12-8</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
         <is>
-          <t>GB/T96.1-2002</t>
+          <t>GB/T6170</t>
         </is>
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>1040300771</t>
+          <t>1040201772</t>
         </is>
       </c>
       <c r="B280" t="n">
-        <v>88</v>
+        <v>12</v>
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Washer 6-200HV; Washer    6-200HV</t>
+          <t>Nut M4-A2-70</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
         <is>
-          <t>GB/T97.1; GB/T97.1-2002</t>
+          <t>GB/T6170-2000</t>
         </is>
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000; Upper Boom Assembly 00773200300000000; Chain System 00773200700000000; Tower Boom Assembly 00773200400000000; Turntable 00773200800000000; Hood 00773201100000000</t>
+          <t>Chain System 00773200700000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F280" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>1040301016</t>
+          <t>1040201865</t>
         </is>
       </c>
       <c r="B281" t="n">
-        <v>37</v>
+        <v>4</v>
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Washer 16-300HV</t>
+          <t>Nut M6-8</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
         <is>
-          <t>GB/T97.1-2002</t>
+          <t>GB/T6170-2000</t>
         </is>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>Slewing Mechanism 00773200900000000</t>
+          <t>Chain System 00773200700000000</t>
+        </is>
+      </c>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>1040301033</t>
+          <t>1040201896</t>
         </is>
       </c>
       <c r="B282" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Washer 20-300HV</t>
+          <t>Nut M6-8</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
         <is>
-          <t>GB/T97.1</t>
+          <t>GB/T889.1; GB/T889.1-2015</t>
         </is>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Work Platform 00773200100000000; Upper Boom Assembly 00773200300000000</t>
+        </is>
+      </c>
+      <c r="F282" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>1040301502</t>
+          <t>1040201902</t>
         </is>
       </c>
       <c r="B283" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="C283" t="inlineStr">
         <is>
-          <t>Washer 10</t>
+          <t>Nut M6-6</t>
         </is>
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>GB/T93-1987</t>
+          <t>GB/T802</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Power Unit Assembly of Turntable 00773205201800000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F283" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>1040301510</t>
+          <t>1040202280</t>
         </is>
       </c>
       <c r="B284" t="n">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>Washer; Washer 8; Screw M6×15-8.8</t>
+          <t>Nut M24-05-DKL</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
         <is>
-          <t>GB/T93-1987 8; GB/T93-1987; GB/T70.1-2000</t>
+          <t>GB/T6181-1986</t>
         </is>
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000; Main valve Assembly of Turntable 00773205201800000; High Pressure Filter installation of Turntable 00773205201800000; Low Pressure Filter Installation of Turntable 00773205201800000; Main Boom Lifting Balance Valve Installation 00773205201000000; Tower Boom Balance Valve Assembly 00773205200600000; Main Boom Telescopic Balance Valve Installation 00773205200800000; Main Boom Platform Valve Installation 00773205200800000; Jib Lifting Balance Valve Assembly 00773205201000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F284" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>1040301511</t>
+          <t>1040202296</t>
         </is>
       </c>
       <c r="B285" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Washer 24-200HV</t>
+          <t>Nut 5/8-18UNF-10(Spiralock)</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
         <is>
-          <t>GB/T97.1; GB/T97.1-2002</t>
+          <t>ANSIB18.2.2-2015</t>
         </is>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000; Counterweight 00773201000000000; Chassis 00773202800000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F285" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>1040301515</t>
+          <t>1040202297</t>
         </is>
       </c>
       <c r="B286" t="n">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Washer 8-200HV; Washer    8-200HV</t>
+          <t>Nut M16×1.5-10 (Spiralock)</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
         <is>
-          <t>GB/T97.1; GB/T97.1-2002</t>
+          <t>GB/T6177.2-2000</t>
         </is>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Jib 00773200200000000; Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000; Turntable 00773200800000000; Chassis 00773202800000000; Main valve Assembly of Turntable 00773205201800000; High Pressure Filter installation of Turntable 00773205201800000; Low Pressure Filter Installation of Turntable 00773205201800000; Main Boom Lifting Balance Valve Installation 00773205201000000; Tower Boom Balance Valve Assembly 00773205200600000; Main Boom Telescopic Balance Valve Installation 00773205200800000; Jib Lifting Balance Valve Assembly 00773205201000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F286" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>1040301610</t>
+          <t>1040300051</t>
         </is>
       </c>
       <c r="B287" t="n">
@@ -6875,57 +8241,67 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Washer 6</t>
+          <t>Washer 6-200HV</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
         <is>
-          <t>GB/T93-1987</t>
+          <t>GB/T97.1-2002</t>
         </is>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>Turntable 00773200800000000</t>
+          <t>Main Boom Platform Valve Installation 00773205200800000</t>
+        </is>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>1040302410</t>
+          <t>1040300062</t>
         </is>
       </c>
       <c r="B288" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Washer    4-200HV</t>
+          <t>Washer 6</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>GB/T97.1-2002</t>
+          <t>GB/T93-1987</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Upper Boom Assembly 00773200300000000; Chain System 00773200700000000</t>
+          <t>Main Boom Platform Valve Installation 00773205200800000</t>
+        </is>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>1040302480</t>
+          <t>1040300735</t>
         </is>
       </c>
       <c r="B289" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>Washer    8-200HV; Washer 8-200HV</t>
+          <t>Washer 6-200HV</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -6935,22 +8311,27 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>Chain System 00773200700000000; Tower Boom Assembly 00773200400000000; Turntable 00773200800000000; Chassis 00773202800000000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F289" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>1040302489</t>
+          <t>1040300771</t>
         </is>
       </c>
       <c r="B290" t="n">
-        <v>48</v>
+        <v>88</v>
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Washer 10-200HV</t>
+          <t>Washer 6-200HV; Washer    6-200HV</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -6960,364 +8341,487 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000; Jib 00773200200000000; Upper Boom Assembly 00773200300000000; Power Unit Assembly of Turntable 00773205201800000</t>
+          <t>Work Platform 00773200100000000; Upper Boom Assembly 00773200300000000; Chain System 00773200700000000; Tower Boom Assembly 00773200400000000; Turntable 00773200800000000; Hood 00773201100000000</t>
+        </is>
+      </c>
+      <c r="F290" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>1040302490</t>
+          <t>1040301016</t>
         </is>
       </c>
       <c r="B291" t="n">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Washer 12-200HV</t>
+          <t>Washer 16-300HV</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
         <is>
-          <t>GB/T97.1; GB/T97.1-2002</t>
+          <t>GB/T97.1-2002</t>
         </is>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000; Jib 00773200200000000; Tower Boom Assembly 00773200400000000</t>
+          <t>Slewing Mechanism 00773200900000000</t>
+        </is>
+      </c>
+      <c r="F291" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>1040302512</t>
+          <t>1040301033</t>
         </is>
       </c>
       <c r="B292" t="n">
-        <v>42</v>
+        <v>1</v>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Washer 10-200HV</t>
+          <t>Washer 20-300HV</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
         <is>
-          <t>GB/T96.1; GB/T96.1-2002</t>
+          <t>GB/T97.1</t>
         </is>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000; Turntable 00773200800000000; Chassis 00773202800000000</t>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F292" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>1040500394</t>
+          <t>1040301502</t>
         </is>
       </c>
       <c r="B293" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Cotter pin</t>
+          <t>Washer 10</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
         <is>
-          <t>GB/T91-2000</t>
+          <t>GB/T93-1987</t>
         </is>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Power Unit Assembly of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F293" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>1089900652</t>
+          <t>1040301510</t>
         </is>
       </c>
       <c r="B294" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Sealing strip</t>
-        </is>
-      </c>
-      <c r="D294" t="inlineStr"/>
+          <t>Washer; Washer 8; Screw M6×15-8.8</t>
+        </is>
+      </c>
+      <c r="D294" t="inlineStr">
+        <is>
+          <t>GB/T93-1987 8; GB/T93-1987; GB/T70.1-2000</t>
+        </is>
+      </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Turntable 00773200800000000; Main valve Assembly of Turntable 00773205201800000; High Pressure Filter installation of Turntable 00773205201800000; Low Pressure Filter Installation of Turntable 00773205201800000; Main Boom Lifting Balance Valve Installation 00773205201000000; Tower Boom Balance Valve Assembly 00773205200600000; Main Boom Telescopic Balance Valve Installation 00773205200800000; Main Boom Platform Valve Installation 00773205200800000; Jib Lifting Balance Valve Assembly 00773205201000000</t>
+        </is>
+      </c>
+      <c r="F294" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>1101000180</t>
+          <t>1040301511</t>
         </is>
       </c>
       <c r="B295" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Lock</t>
-        </is>
-      </c>
-      <c r="D295" t="inlineStr"/>
+          <t>Washer 24-200HV</t>
+        </is>
+      </c>
+      <c r="D295" t="inlineStr">
+        <is>
+          <t>GB/T97.1; GB/T97.1-2002</t>
+        </is>
+      </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Chassis 00773202800000000</t>
+          <t>Jib 00773200200000000; Counterweight 00773201000000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>1109800044</t>
+          <t>1040301515</t>
         </is>
       </c>
       <c r="B296" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Tongue lock</t>
-        </is>
-      </c>
-      <c r="D296" t="inlineStr"/>
+          <t>Washer 8-200HV; Washer    8-200HV</t>
+        </is>
+      </c>
+      <c r="D296" t="inlineStr">
+        <is>
+          <t>GB/T97.1; GB/T97.1-2002</t>
+        </is>
+      </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>Hood 00773201100000000</t>
+          <t>Jib 00773200200000000; Upper Boom Assembly 00773200300000000; Tower Boom Assembly 00773200400000000; Turntable 00773200800000000; Chassis 00773202800000000; Main valve Assembly of Turntable 00773205201800000; High Pressure Filter installation of Turntable 00773205201800000; Low Pressure Filter Installation of Turntable 00773205201800000; Main Boom Lifting Balance Valve Installation 00773205201000000; Tower Boom Balance Valve Assembly 00773205200600000; Main Boom Telescopic Balance Valve Installation 00773205200800000; Jib Lifting Balance Valve Assembly 00773205201000000</t>
+        </is>
+      </c>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>1109900921</t>
+          <t>1040301610</t>
         </is>
       </c>
       <c r="B297" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Rubber plug M36</t>
-        </is>
-      </c>
-      <c r="D297" t="inlineStr"/>
+          <t>Washer 6</t>
+        </is>
+      </c>
+      <c r="D297" t="inlineStr">
+        <is>
+          <t>GB/T93-1987</t>
+        </is>
+      </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Counterweight 00773201000000000</t>
+          <t>Turntable 00773200800000000</t>
+        </is>
+      </c>
+      <c r="F297" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>1109901017</t>
+          <t>1040302410</t>
         </is>
       </c>
       <c r="B298" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Joint link pin 24101.09.2</t>
-        </is>
-      </c>
-      <c r="D298" t="inlineStr"/>
+          <t>Washer    4-200HV</t>
+        </is>
+      </c>
+      <c r="D298" t="inlineStr">
+        <is>
+          <t>GB/T97.1-2002</t>
+        </is>
+      </c>
       <c r="E298" t="inlineStr">
         <is>
-          <t>Chain System 00773200700000000</t>
+          <t>Upper Boom Assembly 00773200300000000; Chain System 00773200700000000</t>
+        </is>
+      </c>
+      <c r="F298" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>1109901018</t>
+          <t>1040302480</t>
         </is>
       </c>
       <c r="B299" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Joint link hole 
-  24101.09.1</t>
-        </is>
-      </c>
-      <c r="D299" t="inlineStr"/>
+          <t>Washer    8-200HV; Washer 8-200HV</t>
+        </is>
+      </c>
+      <c r="D299" t="inlineStr">
+        <is>
+          <t>GB/T96.1-2002</t>
+        </is>
+      </c>
       <c r="E299" t="inlineStr">
         <is>
-          <t>Chain System 00773200700000000</t>
+          <t>Chain System 00773200700000000; Tower Boom Assembly 00773200400000000; Turntable 00773200800000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F299" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>1109901019</t>
+          <t>1040302489</t>
         </is>
       </c>
       <c r="B300" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>Chain sections 2500.09.075.0</t>
-        </is>
-      </c>
-      <c r="D300" t="inlineStr"/>
+          <t>Washer 10-200HV</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>GB/T97.1; GB/T97.1-2002</t>
+        </is>
+      </c>
       <c r="E300" t="inlineStr">
         <is>
-          <t>Chain System 00773200700000000</t>
+          <t>Work Platform 00773200100000000; Jib 00773200200000000; Upper Boom Assembly 00773200300000000; Power Unit Assembly of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F300" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>1109901020</t>
+          <t>1040302490</t>
         </is>
       </c>
       <c r="B301" t="n">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Chain bar 25000.09</t>
-        </is>
-      </c>
-      <c r="D301" t="inlineStr"/>
+          <t>Washer 12-200HV</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>GB/T97.1; GB/T97.1-2002</t>
+        </is>
+      </c>
       <c r="E301" t="inlineStr">
         <is>
-          <t>Chain System 00773200700000000</t>
+          <t>Work Platform 00773200100000000; Jib 00773200200000000; Tower Boom Assembly 00773200400000000</t>
+        </is>
+      </c>
+      <c r="F301" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>1110100355</t>
+          <t>1040302512</t>
         </is>
       </c>
       <c r="B302" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Gas spring</t>
-        </is>
-      </c>
-      <c r="D302" t="inlineStr"/>
+          <t>Washer 10-200HV</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>GB/T96.1; GB/T96.1-2002</t>
+        </is>
+      </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>Hood 00773201100000000</t>
+          <t>Work Platform 00773200100000000; Turntable 00773200800000000; Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F302" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>1140101461</t>
+          <t>1040500394</t>
         </is>
       </c>
       <c r="B303" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Non return joint</t>
-        </is>
-      </c>
-      <c r="D303" t="inlineStr"/>
+          <t>Cotter pin</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>GB/T91-2000</t>
+        </is>
+      </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Power Unit Assembly of Turntable 00773205201800000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F303" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>1140101463</t>
+          <t>1089900652</t>
         </is>
       </c>
       <c r="B304" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
+          <t>Sealing strip</t>
         </is>
       </c>
       <c r="D304" t="inlineStr"/>
       <c r="E304" t="inlineStr">
         <is>
-          <t>High Pressure Filter installation of Turntable 00773205201800000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F304" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>1140101475</t>
+          <t>1101000180</t>
         </is>
       </c>
       <c r="B305" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
+          <t>Lock</t>
         </is>
       </c>
       <c r="D305" t="inlineStr"/>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Main Boom Telescopic Balance Valve Installation 00773205200800000; Platform Rotary Actuator Joint Assembly 00773205201200000; Jib Rotary Actuator Joint Assembly 00773205201200000; Lower Leveling Cylinder Joint Assembly 00773205201200000</t>
+          <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F305" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>1140101476</t>
+          <t>1109800044</t>
         </is>
       </c>
       <c r="B306" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Tube to swivel 
-  M10×30-8.8; Tube to swivel</t>
+          <t>Tongue lock</t>
         </is>
       </c>
       <c r="D306" t="inlineStr"/>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Power Unit Assembly of Turntable 00773205201800000; Rotary Motor Joint Assembly 00773205201200000</t>
+          <t>Hood 00773201100000000</t>
+        </is>
+      </c>
+      <c r="F306" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>1140101477</t>
+          <t>1109900921</t>
         </is>
       </c>
       <c r="B307" t="n">
@@ -7325,20 +8829,25 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
+          <t>Rubber plug M36</t>
         </is>
       </c>
       <c r="D307" t="inlineStr"/>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Low Pressure Filter Installation of Turntable 00773205201800000</t>
+          <t>Counterweight 00773201000000000</t>
+        </is>
+      </c>
+      <c r="F307" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>1140102959</t>
+          <t>1109901017</t>
         </is>
       </c>
       <c r="B308" t="n">
@@ -7346,108 +8855,133 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Tube to swivel</t>
+          <t>Joint link pin 24101.09.2</t>
         </is>
       </c>
       <c r="D308" t="inlineStr"/>
       <c r="E308" t="inlineStr">
         <is>
-          <t>Lower Leveling Cylinder Joint Assembly 00773205201200000</t>
+          <t>Chain System 00773200700000000</t>
+        </is>
+      </c>
+      <c r="F308" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>1140103357</t>
+          <t>1109901018</t>
         </is>
       </c>
       <c r="B309" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Non return joint</t>
+          <t>Joint link hole 24101.09.1</t>
         </is>
       </c>
       <c r="D309" t="inlineStr"/>
       <c r="E309" t="inlineStr">
         <is>
-          <t>Main Boom Platform Valve Installation 00773205200800000; Upper Leveling Cylinder Joint Assembly 00773205201200000</t>
+          <t>Chain System 00773200700000000</t>
+        </is>
+      </c>
+      <c r="F309" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>1140107691</t>
+          <t>1109901019</t>
         </is>
       </c>
       <c r="B310" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Non return adjustable joint</t>
+          <t>Chain sections 2500.09.075.0</t>
         </is>
       </c>
       <c r="D310" t="inlineStr"/>
       <c r="E310" t="inlineStr">
         <is>
-          <t>Platform Rotary Actuator Joint Assembly 00773205201200000; Jib Rotary Actuator Joint Assembly 00773205201200000</t>
+          <t>Chain System 00773200700000000</t>
+        </is>
+      </c>
+      <c r="F310" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>1140107801</t>
+          <t>1109901020</t>
         </is>
       </c>
       <c r="B311" t="n">
-        <v>6</v>
+        <v>36</v>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>45° combined elbow</t>
+          <t>Chain bar 25000.09</t>
         </is>
       </c>
       <c r="D311" t="inlineStr"/>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Main Boom Platform Valve Installation 00773205200800000</t>
+          <t>Chain System 00773200700000000</t>
+        </is>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>1140109052</t>
+          <t>1110100355</t>
         </is>
       </c>
       <c r="B312" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Non return joint</t>
+          <t>Gas spring</t>
         </is>
       </c>
       <c r="D312" t="inlineStr"/>
       <c r="E312" t="inlineStr">
         <is>
-          <t>High Pressure Filter installation of Turntable 00773205201800000</t>
+          <t>Hood 00773201100000000</t>
+        </is>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>1140111237</t>
+          <t>1140101461</t>
         </is>
       </c>
       <c r="B313" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="C313" t="inlineStr">
         <is>
@@ -7457,14 +8991,19 @@
       <c r="D313" t="inlineStr"/>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Main valve Assembly of Turntable 00773205201800000; Main Boom Platform Valve Installation 00773205200800000; Lower Leveling Cylinder Joint Assembly 00773205201200000; Steering Cylinder Joint Assembly 00773205201600000</t>
+          <t>Power Unit Assembly of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F313" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>1140112823</t>
+          <t>1140101463</t>
         </is>
       </c>
       <c r="B314" t="n">
@@ -7472,83 +9011,103 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Non return joint</t>
+          <t>Tube to swivel</t>
         </is>
       </c>
       <c r="D314" t="inlineStr"/>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Rotary Motor Joint Assembly 00773205201200000</t>
+          <t>High Pressure Filter installation of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>1140114040</t>
+          <t>1140101475</t>
         </is>
       </c>
       <c r="B315" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Non return joint</t>
+          <t>Tube to swivel</t>
         </is>
       </c>
       <c r="D315" t="inlineStr"/>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Main valve Assembly of Turntable 00773205201800000</t>
+          <t>Main Boom Telescopic Balance Valve Installation 00773205200800000; Platform Rotary Actuator Joint Assembly 00773205201200000; Jib Rotary Actuator Joint Assembly 00773205201200000; Lower Leveling Cylinder Joint Assembly 00773205201200000</t>
+        </is>
+      </c>
+      <c r="F315" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>1140114187</t>
+          <t>1140101476</t>
         </is>
       </c>
       <c r="B316" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Test joint</t>
+          <t>Tube to swivel M10×30-8.8; Tube to swivel</t>
         </is>
       </c>
       <c r="D316" t="inlineStr"/>
       <c r="E316" t="inlineStr">
         <is>
-          <t>Main valve Assembly of Turntable 00773205201800000</t>
+          <t>Power Unit Assembly of Turntable 00773205201800000; Rotary Motor Joint Assembly 00773205201200000</t>
+        </is>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>1140115524</t>
+          <t>1140101477</t>
         </is>
       </c>
       <c r="B317" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Long non return joint</t>
+          <t>Tube to swivel</t>
         </is>
       </c>
       <c r="D317" t="inlineStr"/>
       <c r="E317" t="inlineStr">
         <is>
-          <t>Power Unit Assembly of Turntable 00773205201800000</t>
+          <t>Low Pressure Filter Installation of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>1140207362</t>
+          <t>1140102959</t>
         </is>
       </c>
       <c r="B318" t="n">
@@ -7556,76 +9115,356 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Non return joint</t>
+          <t>Tube to swivel</t>
         </is>
       </c>
       <c r="D318" t="inlineStr"/>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Low Pressure Filter Installation of Turntable 00773205201800000</t>
+          <t>Lower Leveling Cylinder Joint Assembly 00773205201200000</t>
+        </is>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>1159901036</t>
+          <t>1140103357</t>
         </is>
       </c>
       <c r="B319" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Spring hinge</t>
+          <t>Non return joint</t>
         </is>
       </c>
       <c r="D319" t="inlineStr"/>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Hood 00773201100000000</t>
+          <t>Main Boom Platform Valve Installation 00773205200800000; Upper Leveling Cylinder Joint Assembly 00773205201200000</t>
+        </is>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>1999904986</t>
+          <t>1140107691</t>
         </is>
       </c>
       <c r="B320" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Document box</t>
+          <t>Non return adjustable joint</t>
         </is>
       </c>
       <c r="D320" t="inlineStr"/>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Work Platform 00773200100000000</t>
+          <t>Platform Rotary Actuator Joint Assembly 00773205201200000; Jib Rotary Actuator Joint Assembly 00773205201200000</t>
+        </is>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>204060296</t>
+          <t>1140107801</t>
         </is>
       </c>
       <c r="B321" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Great wall vehicle gear oil</t>
+          <t>45° combined elbow</t>
         </is>
       </c>
       <c r="D321" t="inlineStr"/>
       <c r="E321" t="inlineStr">
         <is>
+          <t>Main Boom Platform Valve Installation 00773205200800000</t>
+        </is>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>1140109052</t>
+        </is>
+      </c>
+      <c r="B322" t="n">
+        <v>2</v>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Non return joint</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr">
+        <is>
+          <t>High Pressure Filter installation of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>1140111237</t>
+        </is>
+      </c>
+      <c r="B323" t="n">
+        <v>20</v>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Non return joint</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr">
+        <is>
+          <t>Main valve Assembly of Turntable 00773205201800000; Main Boom Platform Valve Installation 00773205200800000; Lower Leveling Cylinder Joint Assembly 00773205201200000; Steering Cylinder Joint Assembly 00773205201600000</t>
+        </is>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>1140112823</t>
+        </is>
+      </c>
+      <c r="B324" t="n">
+        <v>2</v>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Non return joint</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr">
+        <is>
+          <t>Rotary Motor Joint Assembly 00773205201200000</t>
+        </is>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>1140114040</t>
+        </is>
+      </c>
+      <c r="B325" t="n">
+        <v>2</v>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Non return joint</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr">
+        <is>
+          <t>Main valve Assembly of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F325" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>1140114187</t>
+        </is>
+      </c>
+      <c r="B326" t="n">
+        <v>1</v>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>Test joint</t>
+        </is>
+      </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr">
+        <is>
+          <t>Main valve Assembly of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F326" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>1140115524</t>
+        </is>
+      </c>
+      <c r="B327" t="n">
+        <v>1</v>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>Long non return joint</t>
+        </is>
+      </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr">
+        <is>
+          <t>Power Unit Assembly of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F327" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>1140207362</t>
+        </is>
+      </c>
+      <c r="B328" t="n">
+        <v>2</v>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>Non return joint</t>
+        </is>
+      </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr">
+        <is>
+          <t>Low Pressure Filter Installation of Turntable 00773205201800000</t>
+        </is>
+      </c>
+      <c r="F328" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>1159901036</t>
+        </is>
+      </c>
+      <c r="B329" t="n">
+        <v>4</v>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>Spring hinge</t>
+        </is>
+      </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>Hood 00773201100000000</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>1999904986</t>
+        </is>
+      </c>
+      <c r="B330" t="n">
+        <v>1</v>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>Document box</t>
+        </is>
+      </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr">
+        <is>
+          <t>Work Platform 00773200100000000</t>
+        </is>
+      </c>
+      <c r="F330" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>204060296</t>
+        </is>
+      </c>
+      <c r="B331" t="n">
+        <v>1</v>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>Great wall vehicle gear oil</t>
+        </is>
+      </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr">
+        <is>
           <t>Chassis 00773202800000000</t>
+        </is>
+      </c>
+      <c r="F331" t="inlineStr">
+        <is>
+          <t>ZA10RJE</t>
         </is>
       </c>
     </row>
